--- a/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
+++ b/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POS_Name_is_null_001</t>
+          <t>POS_Name Is Null_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Name_is_null passes with all required fields populated</t>
+          <t>Verify Name Is Null passes with all required fields populated</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEG_Name_is_null_001</t>
+          <t>NEG_Name Is Null_001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Name_is_null fails with missing required fields</t>
+          <t>Verify Name Is Null fails with missing required fields</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EDGE_Name_is_null_001</t>
+          <t>EDGE_Name Is Null_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Name_is_null handles boundary conditions correctly</t>
+          <t>Verify Name Is Null handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POS_PhoneRule_001</t>
+          <t>POS_Phonerule_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify PhoneRule passes with all required fields populated</t>
+          <t>Verify Phonerule passes with all required fields populated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEG_PhoneRule_001</t>
+          <t>NEG_Phonerule_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify PhoneRule fails with missing required fields</t>
+          <t>Verify Phonerule fails with missing required fields</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EDGE_PhoneRule_001</t>
+          <t>EDGE_Phonerule_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify PhoneRule handles boundary conditions correctly</t>
+          <t>Verify Phonerule handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POS_record_001</t>
+          <t>POS_Phone No Only 10 Digit_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify record passes with valid business rule data</t>
+          <t>Verify Phone No Only 10 Digit passes with all required fields populated</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDGE_record_001</t>
+          <t>NEG_Phone No Only 10 Digit_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Negative Validation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify record handles boundary conditions correctly</t>
+          <t>Verify Phone No Only 10 Digit fails with missing required fields</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1065,22 +1065,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POS_dataframe_001</t>
+          <t>EDGE_Phone No Only 10 Digit_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify dataframe passes with valid business rule data</t>
+          <t>Verify Phone No Only 10 Digit handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dataframe</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1132,22 +1132,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDGE_dataframe_001</t>
+          <t>EDL_Name Is Null_POS_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify dataframe handles boundary conditions correctly</t>
+          <t>Load valid data that should pass Name Is Null validation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dataframe</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EDL_Name_is_null_POS_001</t>
+          <t>EDL_Name Is Null_NEG_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Name_is_null validation</t>
+          <t>Attempt to load invalid data that should fail Name Is Null validation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EDL_Name_is_null_NEG_001</t>
+          <t>EDL_Phonerule_POS_002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Name_is_null validation</t>
+          <t>Load valid data that should pass Phonerule validation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EDL_PhoneRule_POS_002</t>
+          <t>EDL_Phonerule_NEG_002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Load valid data that should pass PhoneRule validation</t>
+          <t>Attempt to load invalid data that should fail Phonerule validation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EDL_PhoneRule_NEG_002</t>
+          <t>EDL_Phone No Only 10 Digit_POS_003</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail PhoneRule validation</t>
+          <t>Load valid data that should pass Phone No Only 10 Digit validation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EDL_record_POS_003</t>
+          <t>EDL_Phone No Only 10 Digit_NEG_003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Load valid data that should pass record validation</t>
+          <t>Attempt to load invalid data that should fail Phone No Only 10 Digit validation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1526,207 +1526,6 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EDL_record_NEG_003</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail record validation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EDL_dataframe_POS_004</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass dataframe validation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EDL_dataframe_NEG_004</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail dataframe validation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1743,10 +1542,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -1783,7 +1582,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1798,7 +1597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1810,7 +1609,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1825,7 +1624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1837,44 +1636,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Phone No Only 10 Digit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>business_rule</t>
+          <t>required_field</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Phone, REGEX</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>business_rule</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
         <is>
           <t>General Business Rule</t>
         </is>
@@ -1975,7 +1755,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1992,7 +1772,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2060,7 +1840,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2111,7 +1891,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2157,7 +1937,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">

--- a/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
+++ b/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POS_Name Is Null_001</t>
+          <t>POS_Name_is_null_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Name Is Null passes with all required fields populated</t>
+          <t>Verify Name_is_null passes with all required fields populated</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEG_Name Is Null_001</t>
+          <t>NEG_Name_is_null_001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Name Is Null fails with missing required fields</t>
+          <t>Verify Name_is_null fails with missing required fields</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EDGE_Name Is Null_001</t>
+          <t>EDGE_Name_is_null_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Name Is Null handles boundary conditions correctly</t>
+          <t>Verify Name_is_null handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POS_Phonerule_001</t>
+          <t>POS_PhoneRule_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify Phonerule passes with all required fields populated</t>
+          <t>Verify PhoneRule passes with all required fields populated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEG_Phonerule_001</t>
+          <t>NEG_PhoneRule_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify Phonerule fails with missing required fields</t>
+          <t>Verify PhoneRule fails with missing required fields</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EDGE_Phonerule_001</t>
+          <t>EDGE_PhoneRule_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify Phonerule handles boundary conditions correctly</t>
+          <t>Verify PhoneRule handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POS_Phone No Only 10 Digit_001</t>
+          <t>POS_record_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Phone No Only 10 Digit passes with all required fields populated</t>
+          <t>Verify record passes with valid business rule data</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>record</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEG_Phone No Only 10 Digit_001</t>
+          <t>EDGE_record_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Negative Validation</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify Phone No Only 10 Digit fails with missing required fields</t>
+          <t>Verify record handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>record</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1065,22 +1065,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EDGE_Phone No Only 10 Digit_001</t>
+          <t>POS_dataframe_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify Phone No Only 10 Digit handles boundary conditions correctly</t>
+          <t>Verify dataframe passes with valid business rule data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>dataframe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1132,22 +1132,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDL_Name Is Null_POS_001</t>
+          <t>EDGE_dataframe_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Name Is Null validation</t>
+          <t>Verify dataframe handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>dataframe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EDL_Name Is Null_NEG_001</t>
+          <t>EDL_Name_is_null_POS_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Name Is Null validation</t>
+          <t>Load valid data that should pass Name_is_null validation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EDL_Phonerule_POS_002</t>
+          <t>EDL_Name_is_null_NEG_001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Phonerule validation</t>
+          <t>Attempt to load invalid data that should fail Name_is_null validation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EDL_Phonerule_NEG_002</t>
+          <t>EDL_PhoneRule_POS_002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Phonerule validation</t>
+          <t>Load valid data that should pass PhoneRule validation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EDL_Phone No Only 10 Digit_POS_003</t>
+          <t>EDL_PhoneRule_NEG_002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Phone No Only 10 Digit validation</t>
+          <t>Attempt to load invalid data that should fail PhoneRule validation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EDL_Phone No Only 10 Digit_NEG_003</t>
+          <t>EDL_record_POS_003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Phone No Only 10 Digit validation</t>
+          <t>Load valid data that should pass record validation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>record</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1526,6 +1526,207 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EDL_record_NEG_003</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail record validation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>record</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EDL_dataframe_POS_004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass dataframe validation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dataframe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EDL_dataframe_NEG_004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail dataframe validation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>dataframe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1542,10 +1743,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -1582,7 +1783,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Name Is Null</t>
+          <t>Name_is_null</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1597,7 +1798,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1609,7 +1810,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Phonerule</t>
+          <t>PhoneRule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1624,7 +1825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1636,25 +1837,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Phone No Only 10 Digit</t>
+          <t>record</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>required_field</t>
+          <t>business_rule</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Phone, REGEX</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dataframe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>business_rule</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>General Business Rule</t>
         </is>
@@ -1755,7 +1975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1772,7 +1992,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1840,7 +2060,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1891,7 +2111,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1937,7 +2157,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">

--- a/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
+++ b/Unit Testing Generates/AkashDev/Account/unitTest_Account.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POS_Name_is_null_001</t>
+          <t>POS_Name Is Null_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Name_is_null passes with all required fields populated</t>
+          <t>Verify Name Is Null passes with all required fields populated</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEG_Name_is_null_001</t>
+          <t>NEG_Name Is Null_001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Name_is_null fails with missing required fields</t>
+          <t>Verify Name Is Null fails with missing required fields</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EDGE_Name_is_null_001</t>
+          <t>EDGE_Name Is Null_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Name_is_null handles boundary conditions correctly</t>
+          <t>Verify Name Is Null handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POS_PhoneRule_001</t>
+          <t>POS_Phonerule_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify PhoneRule passes with all required fields populated</t>
+          <t>Verify Phonerule passes with all required fields populated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEG_PhoneRule_001</t>
+          <t>NEG_Phonerule_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify PhoneRule fails with missing required fields</t>
+          <t>Verify Phonerule fails with missing required fields</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EDGE_PhoneRule_001</t>
+          <t>EDGE_Phonerule_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify PhoneRule handles boundary conditions correctly</t>
+          <t>Verify Phonerule handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POS_record_001</t>
+          <t>EDL_Name Is Null_POS_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify record passes with valid business rule data</t>
+          <t>Load valid data that should pass Name Is Null validation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDGE_record_001</t>
+          <t>EDL_Name Is Null_NEG_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify record handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Name Is Null validation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>record</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1065,22 +1065,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POS_dataframe_001</t>
+          <t>EDL_Phonerule_POS_002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify dataframe passes with valid business rule data</t>
+          <t>Load valid data that should pass Phonerule validation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dataframe</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1132,22 +1132,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDGE_dataframe_001</t>
+          <t>EDL_Phonerule_NEG_002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify dataframe handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Phonerule validation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dataframe</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>genai_driven</t>
+          <t>partial_genai</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1191,542 +1191,6 @@
         </is>
       </c>
       <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EDL_Name_is_null_POS_001</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass Name_is_null validation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Name_is_null</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EDL_Name_is_null_NEG_001</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail Name_is_null validation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Name_is_null</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>EDL_PhoneRule_POS_002</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass PhoneRule validation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PhoneRule</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>EDL_PhoneRule_NEG_002</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail PhoneRule validation</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PhoneRule</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EDL_record_POS_003</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass record validation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EDL_record_NEG_003</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail record validation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EDL_dataframe_POS_004</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass dataframe validation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EDL_dataframe_NEG_004</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail dataframe validation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1743,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1783,7 +1247,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Name_is_null</t>
+          <t>Name Is Null</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1798,7 +1262,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1810,7 +1274,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PhoneRule</t>
+          <t>Phonerule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1825,56 +1289,10 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>record</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>business_rule</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>business_rule</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
         <is>
           <t>General Business Rule</t>
         </is>
@@ -1975,7 +1393,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1992,7 +1410,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2060,7 +1478,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2111,7 +1529,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2157,7 +1575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
